--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99A91430-A535-43EC-B51C-54B23DF16830}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{844A44E1-AAFC-4B08-B897-9623E483BB36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="99">
   <si>
     <t>Year</t>
   </si>
@@ -325,6 +325,9 @@
   </si>
   <si>
     <t>current_link</t>
+  </si>
+  <si>
+    <t>https://forms.gle/yADwS2mSjrevJKuC9</t>
   </si>
 </sst>
 </file>
@@ -660,42 +663,42 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AE12"/>
-  <sheetFormatPr defaultColWidth="21.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="21.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.7265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.7265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.7265625" customWidth="1"/>
-    <col min="7" max="7" width="37.1796875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.1796875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.1796875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.81640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.26953125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="29.453125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.7109375" customWidth="1"/>
+    <col min="7" max="7" width="37.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.7109375" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="6" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="16" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="20.1796875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="20.140625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="23" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="19.26953125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="48.81640625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="39.453125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="48.85546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="39.42578125" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="28" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="43.7265625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="42.54296875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="26.26953125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="22.81640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="43.7109375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="42.5703125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="26.28515625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="22.85546875" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="35" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="35" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="35" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="11.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -790,7 +793,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2016</v>
       </c>
@@ -807,7 +810,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2017</v>
       </c>
@@ -824,7 +827,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2018</v>
       </c>
@@ -841,7 +844,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2019</v>
       </c>
@@ -861,7 +864,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2020</v>
       </c>
@@ -881,7 +884,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2021</v>
       </c>
@@ -904,7 +907,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2022</v>
       </c>
@@ -930,7 +933,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2023</v>
       </c>
@@ -956,7 +959,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2024</v>
       </c>
@@ -997,7 +1000,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2025</v>
       </c>
@@ -1080,7 +1083,7 @@
         <v>459403</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2026</v>
       </c>
@@ -1098,6 +1101,9 @@
       </c>
       <c r="F12" t="s">
         <v>96</v>
+      </c>
+      <c r="G12" t="s">
+        <v>98</v>
       </c>
       <c r="H12" t="s">
         <v>34</v>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{844A44E1-AAFC-4B08-B897-9623E483BB36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2FD9444-03F5-48D4-B289-0B3CF00A2419}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2FD9444-03F5-48D4-B289-0B3CF00A2419}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27A499A2-CAD1-4990-AA86-F9A8D8030499}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -303,9 +303,6 @@
     <t>11th EFSPI regulatory statistics workshop</t>
   </si>
   <si>
-    <t>not available yet</t>
-  </si>
-  <si>
     <t>data/2026/11th EFSPI RegStat Workshop program.pdf</t>
   </si>
   <si>
@@ -328,6 +325,9 @@
   </si>
   <si>
     <t>https://forms.gle/yADwS2mSjrevJKuC9</t>
+  </si>
+  <si>
+    <t>2nd March 2026</t>
   </si>
 </sst>
 </file>
@@ -715,7 +715,7 @@
         <v>39</v>
       </c>
       <c r="F1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G1" t="s">
         <v>22</v>
@@ -1094,16 +1094,16 @@
         <v>89</v>
       </c>
       <c r="D12" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="E12" t="s">
         <v>83</v>
       </c>
       <c r="F12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H12" t="s">
         <v>34</v>
@@ -1127,7 +1127,7 @@
         <v>100</v>
       </c>
       <c r="O12" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P12" t="s">
         <v>84</v>
@@ -1139,22 +1139,22 @@
         <v>86</v>
       </c>
       <c r="S12" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="T12" t="s">
         <v>87</v>
       </c>
       <c r="V12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="W12" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="X12" t="s">
         <v>94</v>
       </c>
-      <c r="X12" t="s">
-        <v>95</v>
-      </c>
       <c r="Y12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27A499A2-CAD1-4990-AA86-F9A8D8030499}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB8F1DDA-2378-449F-829F-846CF4620BDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="100">
   <si>
     <t>Year</t>
   </si>
@@ -328,6 +328,9 @@
   </si>
   <si>
     <t>2nd March 2026</t>
+  </si>
+  <si>
+    <t>Merck KGaA</t>
   </si>
 </sst>
 </file>
@@ -663,42 +666,42 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AE12"/>
-  <sheetFormatPr defaultColWidth="21.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="21.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.7109375" customWidth="1"/>
-    <col min="7" max="7" width="37.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="29.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.7265625" customWidth="1"/>
+    <col min="7" max="7" width="37.1796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.1796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.81640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.26953125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="29.453125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.7265625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="6" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="16" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="20.1796875" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="23" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="48.85546875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="39.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="19.26953125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="48.81640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="39.453125" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="28" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="43.7109375" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="42.5703125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="26.28515625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="43.7265625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="42.54296875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="26.26953125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="22.81640625" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="35" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11.1796875" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="35" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="11.1796875" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="35" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="11.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -793,7 +796,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>2016</v>
       </c>
@@ -810,7 +813,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2017</v>
       </c>
@@ -827,7 +830,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>2018</v>
       </c>
@@ -844,7 +847,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>2019</v>
       </c>
@@ -864,7 +867,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>2020</v>
       </c>
@@ -884,7 +887,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>2021</v>
       </c>
@@ -907,7 +910,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>2022</v>
       </c>
@@ -933,7 +936,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>2023</v>
       </c>
@@ -959,7 +962,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>2024</v>
       </c>
@@ -1000,7 +1003,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>2025</v>
       </c>
@@ -1083,7 +1086,7 @@
         <v>459403</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>2026</v>
       </c>
@@ -1154,7 +1157,7 @@
         <v>94</v>
       </c>
       <c r="Y12" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB8F1DDA-2378-449F-829F-846CF4620BDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AA7685D-0F5D-4FF1-9A74-20717C19784B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -315,9 +315,6 @@
     <t>https://ww2.amstat.org/meetings/risw/2026/</t>
   </si>
   <si>
-    <t>none yet</t>
-  </si>
-  <si>
     <t>[here](2026.html)</t>
   </si>
   <si>
@@ -330,7 +327,10 @@
     <t>2nd March 2026</t>
   </si>
   <si>
-    <t>Merck KGaA</t>
+    <t>Merck KGaA, Bayer</t>
+  </si>
+  <si>
+    <t>Novartis</t>
   </si>
 </sst>
 </file>
@@ -718,7 +718,7 @@
         <v>39</v>
       </c>
       <c r="F1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G1" t="s">
         <v>22</v>
@@ -1097,16 +1097,16 @@
         <v>89</v>
       </c>
       <c r="D12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E12" t="s">
         <v>83</v>
       </c>
       <c r="F12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H12" t="s">
         <v>34</v>
@@ -1154,10 +1154,10 @@
         <v>93</v>
       </c>
       <c r="X12" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="Y12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AA7685D-0F5D-4FF1-9A74-20717C19784B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECFB8B5A-E295-4D1B-A5E6-11021FFDECBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -327,10 +327,10 @@
     <t>2nd March 2026</t>
   </si>
   <si>
-    <t>Merck KGaA, Bayer</t>
-  </si>
-  <si>
     <t>Novartis</t>
+  </si>
+  <si>
+    <t>Merck KGaA, Bayer, Novo Nordisk</t>
   </si>
 </sst>
 </file>
@@ -1154,10 +1154,10 @@
         <v>93</v>
       </c>
       <c r="X12" t="s">
+        <v>98</v>
+      </c>
+      <c r="Y12" t="s">
         <v>99</v>
-      </c>
-      <c r="Y12" t="s">
-        <v>98</v>
       </c>
     </row>
   </sheetData>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECFB8B5A-E295-4D1B-A5E6-11021FFDECBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED052EDA-868E-430B-AEFE-C9157827E6C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -327,10 +327,10 @@
     <t>2nd March 2026</t>
   </si>
   <si>
-    <t>Novartis</t>
-  </si>
-  <si>
     <t>Merck KGaA, Bayer, Novo Nordisk</t>
+  </si>
+  <si>
+    <t>Novartis, Roche</t>
   </si>
 </sst>
 </file>
@@ -1154,10 +1154,10 @@
         <v>93</v>
       </c>
       <c r="X12" t="s">
+        <v>99</v>
+      </c>
+      <c r="Y12" t="s">
         <v>98</v>
-      </c>
-      <c r="Y12" t="s">
-        <v>99</v>
       </c>
     </row>
   </sheetData>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED052EDA-868E-430B-AEFE-C9157827E6C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF55286A-F3A9-43D6-9440-AFAAEEF041AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -324,13 +324,13 @@
     <t>https://forms.gle/yADwS2mSjrevJKuC9</t>
   </si>
   <si>
-    <t>2nd March 2026</t>
-  </si>
-  <si>
     <t>Merck KGaA, Bayer, Novo Nordisk</t>
   </si>
   <si>
     <t>Novartis, Roche</t>
+  </si>
+  <si>
+    <t>22nd April</t>
   </si>
 </sst>
 </file>
@@ -666,42 +666,42 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AE12"/>
-  <sheetFormatPr defaultColWidth="21.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="21.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.7265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.7265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.7265625" customWidth="1"/>
-    <col min="7" max="7" width="37.1796875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.1796875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.1796875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.81640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.26953125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="29.453125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.7109375" customWidth="1"/>
+    <col min="7" max="7" width="37.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.7109375" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="6" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="16" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="20.1796875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="20.140625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="23" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="19.26953125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="48.81640625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="39.453125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="48.85546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="39.42578125" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="28" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="43.7265625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="42.54296875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="26.26953125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="22.81640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="43.7109375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="42.5703125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="26.28515625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="22.85546875" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="35" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="35" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="35" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="11.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -796,7 +796,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2016</v>
       </c>
@@ -813,7 +813,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2017</v>
       </c>
@@ -830,7 +830,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2018</v>
       </c>
@@ -847,7 +847,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2019</v>
       </c>
@@ -867,7 +867,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2020</v>
       </c>
@@ -887,7 +887,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2021</v>
       </c>
@@ -910,7 +910,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2022</v>
       </c>
@@ -936,7 +936,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2023</v>
       </c>
@@ -962,7 +962,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2024</v>
       </c>
@@ -1003,7 +1003,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2025</v>
       </c>
@@ -1086,7 +1086,7 @@
         <v>459403</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2026</v>
       </c>
@@ -1097,7 +1097,7 @@
         <v>89</v>
       </c>
       <c r="D12" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E12" t="s">
         <v>83</v>
@@ -1154,10 +1154,10 @@
         <v>93</v>
       </c>
       <c r="X12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Y12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF55286A-F3A9-43D6-9440-AFAAEEF041AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3630FB5E-D7A3-4CFD-BD1C-2F98E53677F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -330,7 +330,7 @@
     <t>Novartis, Roche</t>
   </si>
   <si>
-    <t>22nd April</t>
+    <t>24th April</t>
   </si>
 </sst>
 </file>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3630FB5E-D7A3-4CFD-BD1C-2F98E53677F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{245EC4B0-7A80-4A31-9145-C5904B718DC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -330,7 +330,7 @@
     <t>Novartis, Roche</t>
   </si>
   <si>
-    <t>24th April</t>
+    <t>30th April 2026</t>
   </si>
 </sst>
 </file>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{245EC4B0-7A80-4A31-9145-C5904B718DC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A055738-042D-47ED-B2CF-4E1F9EA1B1B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -330,7 +330,7 @@
     <t>Novartis, Roche</t>
   </si>
   <si>
-    <t>30th April 2026</t>
+    <t>12th May 2026</t>
   </si>
 </sst>
 </file>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A055738-042D-47ED-B2CF-4E1F9EA1B1B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4F66A9F-9BBB-425A-975D-A819ABFD2AB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -330,7 +330,7 @@
     <t>Novartis, Roche</t>
   </si>
   <si>
-    <t>12th May 2026</t>
+    <t>18th May 2026</t>
   </si>
 </sst>
 </file>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4F66A9F-9BBB-425A-975D-A819ABFD2AB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFD161E4-5361-4955-AA72-6020A91FC988}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -330,7 +330,7 @@
     <t>Novartis, Roche</t>
   </si>
   <si>
-    <t>18th May 2026</t>
+    <t>22th May 2026</t>
   </si>
 </sst>
 </file>
@@ -666,42 +666,42 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AE12"/>
-  <sheetFormatPr defaultColWidth="21.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="21.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.7109375" customWidth="1"/>
-    <col min="7" max="7" width="37.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="29.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.7265625" customWidth="1"/>
+    <col min="7" max="7" width="37.1796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.1796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.81640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.26953125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="29.453125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.7265625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="6" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="16" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="20.1796875" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="23" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="48.85546875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="39.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="19.26953125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="48.81640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="39.453125" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="28" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="43.7109375" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="42.5703125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="26.28515625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="43.7265625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="42.54296875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="26.26953125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="22.81640625" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="35" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11.1796875" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="35" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="11.1796875" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="35" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="11.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -796,7 +796,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>2016</v>
       </c>
@@ -813,7 +813,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2017</v>
       </c>
@@ -830,7 +830,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>2018</v>
       </c>
@@ -847,7 +847,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>2019</v>
       </c>
@@ -867,7 +867,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>2020</v>
       </c>
@@ -887,7 +887,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>2021</v>
       </c>
@@ -910,7 +910,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>2022</v>
       </c>
@@ -936,7 +936,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>2023</v>
       </c>
@@ -962,7 +962,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>2024</v>
       </c>
@@ -1003,7 +1003,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>2025</v>
       </c>
@@ -1086,7 +1086,7 @@
         <v>459403</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>2026</v>
       </c>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFD161E4-5361-4955-AA72-6020A91FC988}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C23FCECB-7208-4726-A28F-3032486C5105}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -330,7 +330,7 @@
     <t>Novartis, Roche</t>
   </si>
   <si>
-    <t>22th May 2026</t>
+    <t>27th May 2026</t>
   </si>
 </sst>
 </file>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C23FCECB-7208-4726-A28F-3032486C5105}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C81ED16-3138-4324-8F81-5513416B6394}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -330,7 +330,7 @@
     <t>Novartis, Roche</t>
   </si>
   <si>
-    <t>27th May 2026</t>
+    <t>1st June 2026</t>
   </si>
 </sst>
 </file>
@@ -666,42 +666,42 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AE12"/>
-  <sheetFormatPr defaultColWidth="21.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="21.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.7265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.7265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.7265625" customWidth="1"/>
-    <col min="7" max="7" width="37.1796875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.1796875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.1796875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.81640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.26953125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="29.453125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.7109375" customWidth="1"/>
+    <col min="7" max="7" width="37.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.7109375" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="6" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="16" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="20.1796875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="20.140625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="23" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="19.26953125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="48.81640625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="39.453125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="48.85546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="39.42578125" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="28" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="43.7265625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="42.54296875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="26.26953125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="22.81640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="43.7109375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="42.5703125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="26.28515625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="22.85546875" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="35" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="35" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="35" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="11.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -796,7 +796,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2016</v>
       </c>
@@ -813,7 +813,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2017</v>
       </c>
@@ -830,7 +830,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2018</v>
       </c>
@@ -847,7 +847,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2019</v>
       </c>
@@ -867,7 +867,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2020</v>
       </c>
@@ -887,7 +887,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2021</v>
       </c>
@@ -910,7 +910,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2022</v>
       </c>
@@ -936,7 +936,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2023</v>
       </c>
@@ -962,7 +962,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2024</v>
       </c>
@@ -1003,7 +1003,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2025</v>
       </c>
@@ -1086,7 +1086,7 @@
         <v>459403</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2026</v>
       </c>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C81ED16-3138-4324-8F81-5513416B6394}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E93AF7C1-B167-48B9-910B-F0D16D3D3A39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="101">
   <si>
     <t>Year</t>
   </si>
@@ -331,6 +331,9 @@
   </si>
   <si>
     <t>1st June 2026</t>
+  </si>
+  <si>
+    <t>vivian.lanius@boehringer-ingelheim.com</t>
   </si>
 </sst>
 </file>
@@ -1115,7 +1118,7 @@
         <v>35</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="K12" t="s">
         <v>61</v>
@@ -1167,10 +1170,9 @@
     <hyperlink ref="J11" r:id="rId2" xr:uid="{AC1AD04E-A23E-4238-AEC3-41961624FF1E}"/>
     <hyperlink ref="T2" r:id="rId3" xr:uid="{63D3F9EF-A6C3-4658-B195-A3CD6DE0E7D7}"/>
     <hyperlink ref="T3:T8" r:id="rId4" display="https://www.efspi.org/past-workshops-2/" xr:uid="{0196FBA2-38E1-4621-BF47-4E708FD0EDD1}"/>
-    <hyperlink ref="J12" r:id="rId5" xr:uid="{CF6D3815-16F2-4234-A2EA-8ED8E350CD07}"/>
-    <hyperlink ref="W12" r:id="rId6" xr:uid="{C011DFE0-E0DB-4A84-97EB-7866DAED249D}"/>
+    <hyperlink ref="W12" r:id="rId5" xr:uid="{C011DFE0-E0DB-4A84-97EB-7866DAED249D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId7"/>
+  <pageSetup orientation="portrait" r:id="rId6"/>
 </worksheet>
 </file>
--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E93AF7C1-B167-48B9-910B-F0D16D3D3A39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{363B203D-2B9C-488A-B350-B28664B426FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -330,10 +330,10 @@
     <t>Novartis, Roche</t>
   </si>
   <si>
-    <t>1st June 2026</t>
-  </si>
-  <si>
     <t>vivian.lanius@boehringer-ingelheim.com</t>
+  </si>
+  <si>
+    <t>29th June 2026</t>
   </si>
 </sst>
 </file>
@@ -1100,7 +1100,7 @@
         <v>89</v>
       </c>
       <c r="D12" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E12" t="s">
         <v>83</v>
@@ -1118,7 +1118,7 @@
         <v>35</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K12" t="s">
         <v>61</v>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -5,7 +5,7 @@
   <workbookPr filterPrivacy="1"/>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{363B203D-2B9C-488A-B350-B28664B426FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -669,42 +669,42 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AE12"/>
-  <sheetFormatPr defaultColWidth="21.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="21.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.7109375" customWidth="1"/>
-    <col min="7" max="7" width="37.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="29.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.7265625" customWidth="1"/>
+    <col min="7" max="7" width="37.1796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.1796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.81640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.26953125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="29.453125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.7265625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="6" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="16" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="20.1796875" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="23" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="48.85546875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="39.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="19.26953125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="48.81640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="39.453125" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="28" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="43.7109375" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="42.5703125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="26.28515625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="43.7265625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="42.54296875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="26.26953125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="22.81640625" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="35" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11.1796875" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="35" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="11.1796875" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="35" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="11.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -799,7 +799,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>2016</v>
       </c>
@@ -816,7 +816,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2017</v>
       </c>
@@ -833,7 +833,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>2018</v>
       </c>
@@ -850,7 +850,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>2019</v>
       </c>
@@ -870,7 +870,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>2020</v>
       </c>
@@ -890,7 +890,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>2021</v>
       </c>
@@ -913,7 +913,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>2022</v>
       </c>
@@ -939,7 +939,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>2023</v>
       </c>
@@ -965,7 +965,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>2024</v>
       </c>
@@ -1006,7 +1006,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>2025</v>
       </c>
@@ -1089,7 +1089,7 @@
         <v>459403</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>2026</v>
       </c>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{363B203D-2B9C-488A-B350-B28664B426FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{824FD711-9EEB-4BC6-9F1F-4FDD1611D4F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -333,7 +333,7 @@
     <t>vivian.lanius@boehringer-ingelheim.com</t>
   </si>
   <si>
-    <t>29th June 2026</t>
+    <t>7th July 2026</t>
   </si>
 </sst>
 </file>
@@ -669,42 +669,42 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AE12"/>
-  <sheetFormatPr defaultColWidth="21.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="21.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.7265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.7265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.7265625" customWidth="1"/>
-    <col min="7" max="7" width="37.1796875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.1796875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.1796875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.81640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.26953125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="29.453125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.7109375" customWidth="1"/>
+    <col min="7" max="7" width="37.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.7109375" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="6" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="16" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="20.1796875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="20.140625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="23" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="19.26953125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="48.81640625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="39.453125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="48.85546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="39.42578125" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="28" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="43.7265625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="42.54296875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="26.26953125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="22.81640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="43.7109375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="42.5703125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="26.28515625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="22.85546875" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="35" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="35" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="35" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="11.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -799,7 +799,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2016</v>
       </c>
@@ -816,7 +816,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2017</v>
       </c>
@@ -833,7 +833,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2018</v>
       </c>
@@ -850,7 +850,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2019</v>
       </c>
@@ -870,7 +870,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2020</v>
       </c>
@@ -890,7 +890,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2021</v>
       </c>
@@ -913,7 +913,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2022</v>
       </c>
@@ -939,7 +939,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2023</v>
       </c>
@@ -965,7 +965,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2024</v>
       </c>
@@ -1006,7 +1006,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2025</v>
       </c>
@@ -1089,7 +1089,7 @@
         <v>459403</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2026</v>
       </c>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{824FD711-9EEB-4BC6-9F1F-4FDD1611D4F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C000BE45-5BA0-400B-BA55-B17C51F53327}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -333,7 +333,7 @@
     <t>vivian.lanius@boehringer-ingelheim.com</t>
   </si>
   <si>
-    <t>7th July 2026</t>
+    <t>20th July 2026</t>
   </si>
 </sst>
 </file>
@@ -669,42 +669,42 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AE12"/>
-  <sheetFormatPr defaultColWidth="21.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="21.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.7109375" customWidth="1"/>
-    <col min="7" max="7" width="37.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="29.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.7265625" customWidth="1"/>
+    <col min="7" max="7" width="37.1796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.1796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.81640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.26953125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="29.453125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.7265625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="6" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="16" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="20.1796875" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="23" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="48.85546875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="39.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="19.26953125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="48.81640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="39.453125" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="28" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="43.7109375" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="42.5703125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="26.28515625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="43.7265625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="42.54296875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="26.26953125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="22.81640625" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="35" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11.1796875" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="35" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="11.1796875" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="35" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="11.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -799,7 +799,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>2016</v>
       </c>
@@ -816,7 +816,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2017</v>
       </c>
@@ -833,7 +833,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>2018</v>
       </c>
@@ -850,7 +850,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>2019</v>
       </c>
@@ -870,7 +870,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>2020</v>
       </c>
@@ -890,7 +890,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>2021</v>
       </c>
@@ -913,7 +913,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>2022</v>
       </c>
@@ -939,7 +939,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>2023</v>
       </c>
@@ -965,7 +965,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>2024</v>
       </c>
@@ -1006,7 +1006,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>2025</v>
       </c>
@@ -1089,7 +1089,7 @@
         <v>459403</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>2026</v>
       </c>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C000BE45-5BA0-400B-BA55-B17C51F53327}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{816E7720-B0B6-4733-B5FF-58C4EB47FC36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -333,7 +333,7 @@
     <t>vivian.lanius@boehringer-ingelheim.com</t>
   </si>
   <si>
-    <t>20th July 2026</t>
+    <t>28th July 2026</t>
   </si>
 </sst>
 </file>
@@ -669,42 +669,42 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AE12"/>
-  <sheetFormatPr defaultColWidth="21.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="21.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.7265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.7265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.7265625" customWidth="1"/>
-    <col min="7" max="7" width="37.1796875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.1796875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.1796875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.81640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.26953125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="29.453125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.7109375" customWidth="1"/>
+    <col min="7" max="7" width="37.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.7109375" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="6" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="16" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="20.1796875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="20.140625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="23" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="19.26953125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="48.81640625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="39.453125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="48.85546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="39.42578125" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="28" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="43.7265625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="42.54296875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="26.26953125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="22.81640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="43.7109375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="42.5703125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="26.28515625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="22.85546875" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="35" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="35" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="35" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="11.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -799,7 +799,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2016</v>
       </c>
@@ -816,7 +816,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2017</v>
       </c>
@@ -833,7 +833,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2018</v>
       </c>
@@ -850,7 +850,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2019</v>
       </c>
@@ -870,7 +870,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2020</v>
       </c>
@@ -890,7 +890,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2021</v>
       </c>
@@ -913,7 +913,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2022</v>
       </c>
@@ -939,7 +939,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2023</v>
       </c>
@@ -965,7 +965,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2024</v>
       </c>
@@ -1006,7 +1006,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2025</v>
       </c>
@@ -1089,7 +1089,7 @@
         <v>459403</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2026</v>
       </c>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{816E7720-B0B6-4733-B5FF-58C4EB47FC36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB00914E-541C-4FC1-9587-A89F25DECAA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -321,9 +321,6 @@
     <t>current_link</t>
   </si>
   <si>
-    <t>https://forms.gle/yADwS2mSjrevJKuC9</t>
-  </si>
-  <si>
     <t>Merck KGaA, Bayer, Novo Nordisk</t>
   </si>
   <si>
@@ -334,6 +331,9 @@
   </si>
   <si>
     <t>28th July 2026</t>
+  </si>
+  <si>
+    <t>https://forms.gle/jpMHRju973GEzDXPA</t>
   </si>
 </sst>
 </file>
@@ -669,42 +669,42 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AE12"/>
-  <sheetFormatPr defaultColWidth="21.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="21.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.7109375" customWidth="1"/>
-    <col min="7" max="7" width="37.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="29.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.7265625" customWidth="1"/>
+    <col min="7" max="7" width="37.1796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.1796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.81640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.26953125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="29.453125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.7265625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="6" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="16" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="20.1796875" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="23" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="48.85546875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="39.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="19.26953125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="48.81640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="39.453125" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="28" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="43.7109375" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="42.5703125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="26.28515625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="43.7265625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="42.54296875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="26.26953125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="22.81640625" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="35" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11.1796875" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="35" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="11.1796875" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="35" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="11.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -799,7 +799,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>2016</v>
       </c>
@@ -816,7 +816,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2017</v>
       </c>
@@ -833,7 +833,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>2018</v>
       </c>
@@ -850,7 +850,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>2019</v>
       </c>
@@ -870,7 +870,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>2020</v>
       </c>
@@ -890,7 +890,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>2021</v>
       </c>
@@ -913,7 +913,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>2022</v>
       </c>
@@ -939,7 +939,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>2023</v>
       </c>
@@ -965,7 +965,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>2024</v>
       </c>
@@ -1006,7 +1006,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>2025</v>
       </c>
@@ -1089,7 +1089,7 @@
         <v>459403</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>2026</v>
       </c>
@@ -1100,7 +1100,7 @@
         <v>89</v>
       </c>
       <c r="D12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E12" t="s">
         <v>83</v>
@@ -1109,7 +1109,7 @@
         <v>94</v>
       </c>
       <c r="G12" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="H12" t="s">
         <v>34</v>
@@ -1118,7 +1118,7 @@
         <v>35</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K12" t="s">
         <v>61</v>
@@ -1157,10 +1157,10 @@
         <v>93</v>
       </c>
       <c r="X12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="Y12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB00914E-541C-4FC1-9587-A89F25DECAA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14721DA8-AF7B-41F9-82D7-839694D3F93F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -333,7 +333,7 @@
     <t>28th July 2026</t>
   </si>
   <si>
-    <t>https://forms.gle/jpMHRju973GEzDXPA</t>
+    <t>https://forms.gle/WfM1YV8kEnd3zSxi8</t>
   </si>
 </sst>
 </file>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14721DA8-AF7B-41F9-82D7-839694D3F93F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B253691-5C58-4EBE-925E-68675FFE1D00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -333,7 +333,7 @@
     <t>28th July 2026</t>
   </si>
   <si>
-    <t>https://forms.gle/WfM1YV8kEnd3zSxi8</t>
+    <t>https://forms.gle/sozZnsJmkSaZ3uv49</t>
   </si>
 </sst>
 </file>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B253691-5C58-4EBE-925E-68675FFE1D00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{733C692E-F0ED-4C1A-BECC-6D347778CBC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -330,10 +330,10 @@
     <t>vivian.lanius@boehringer-ingelheim.com</t>
   </si>
   <si>
-    <t>28th July 2026</t>
-  </si>
-  <si>
     <t>https://forms.gle/sozZnsJmkSaZ3uv49</t>
+  </si>
+  <si>
+    <t>5th August</t>
   </si>
 </sst>
 </file>
@@ -1100,7 +1100,7 @@
         <v>89</v>
       </c>
       <c r="D12" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E12" t="s">
         <v>83</v>
@@ -1109,7 +1109,7 @@
         <v>94</v>
       </c>
       <c r="G12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H12" t="s">
         <v>34</v>
